--- a/product_selector_out/STM32U375-385 - diff.xlsx
+++ b/product_selector_out/STM32U375-385 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="18">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>33||37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>33||37 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -1834,22 +1834,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1861,67 +1857,59 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -1933,69 +1921,81 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33||35||37</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33, 35, 37</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>33||35||37 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>33||35||37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>33, 35, 37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -2142,17 +2142,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>33||35||37 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2169,22 +2169,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2196,95 +2192,99 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2377,22 +2377,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2404,61 +2400,57 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>47, 51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>47||51 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2468,46 +2460,46 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2517,7 +2509,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2525,55 +2517,63 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2585,22 +2585,18 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2612,29 +2608,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2644,7 +2636,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2652,97 +2644,97 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>79||82</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>79, 82</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>79||82 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2760,16 +2752,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2779,7 +2771,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2787,54 +2779,50 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -2843,320 +2831,8 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32U375VE</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>79||82</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>79, 82</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>79||82 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>STM32U375VG</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E114"/>
+  <autoFilter ref="A18:E102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U375-385 - diff.xlsx
+++ b/product_selector_out/STM32U375-385 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="18">
@@ -1337,18 +1337,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1||2</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1360,99 +1364,95 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1||2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1464,17 +1464,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -1518,17 +1518,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>26 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -1599,17 +1599,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>26 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -1626,18 +1626,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1649,99 +1653,95 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -1834,18 +1834,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1857,59 +1861,67 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -1921,81 +1933,69 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>33||35||37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>33, 35, 37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>33||35||37 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33||35||37</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33, 35, 37</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -2142,17 +2142,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>33||35||37 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2169,18 +2169,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2192,99 +2196,95 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2377,18 +2377,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2400,99 +2404,95 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2585,18 +2585,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2608,99 +2612,95 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -2793,18 +2793,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2816,23 +2820,100 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E102"/>
+  <autoFilter ref="A18:E105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U375-385 - diff.xlsx
+++ b/product_selector_out/STM32U375-385 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>768</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="18">
@@ -1089,27 +1089,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1134,9 +1130,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1149,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1161,9 +1157,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1175,22 +1171,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>47||51||52</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>47, 51</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>47, 51, 52</t>
+          <t>47||51||52</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1215,9 +1211,9 @@
           <t>47, 51</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1230,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>47||51||52 (workbook and API agree)</t>
+          <t>47, 51, 52</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1242,9 +1238,9 @@
           <t>47, 51</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1256,22 +1252,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>47||51||52 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>47, 51</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1296,9 +1292,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1311,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1323,9 +1319,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1333,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1||2</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1350,9 +1346,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1365,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1, 2</t>
+          <t>1||2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1377,9 +1373,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1392,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1||2 (workbook and API agree)</t>
+          <t>1, 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1404,9 +1400,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1418,18 +1414,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1||2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1441,13 +1441,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1459,54 +1459,46 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1515,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1531,9 +1523,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1545,22 +1537,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1572,22 +1564,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1596,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>26 (workbook and API agree)</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1612,9 +1604,9 @@
           <t>25</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1626,22 +1618,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1645,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1677,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1693,9 +1685,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1707,18 +1699,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1730,99 +1726,91 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1822,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1844,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -1861,7 +1849,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1871,7 +1859,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -1888,7 +1876,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1898,7 +1886,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -1915,18 +1903,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1938,59 +1930,67 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -2002,108 +2002,92 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>33||35||37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>33, 37</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2099,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>33, 35, 37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>33, 37</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2142,22 +2126,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>33||35||37 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>33, 37</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2169,22 +2153,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2196,22 +2180,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33||35||37</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>33, 37</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2223,22 +2207,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>33, 35, 37</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>33, 37</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2250,18 +2234,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>33||35||37 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>33, 37</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2273,30 +2261,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2306,120 +2298,108 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2431,22 +2411,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2458,18 +2438,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2481,30 +2465,34 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2514,7 +2502,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -2526,12 +2514,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2541,7 +2529,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -2553,12 +2541,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2568,7 +2556,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2580,81 +2568,69 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2666,18 +2642,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2689,25 +2669,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2717,7 +2701,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2725,21 +2709,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2749,46 +2733,46 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2798,7 +2782,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2806,81 +2790,73 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -2897,23 +2873,231 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E105"/>
+  <autoFilter ref="A18:E113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>